--- a/src/test/resources/excel/menuIPS/datosMenuIPS.xlsx
+++ b/src/test/resources/excel/menuIPS/datosMenuIPS.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\automatizacion\portal Famisanar\src\test\resources\excel\menuIPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC77895-02C5-4AA9-983C-D4065A749890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="4" r:id="rId1"/>
@@ -18,18 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="237">
   <si>
     <t>52102459</t>
   </si>
   <si>
     <t>CC</t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
-    <t>106991234</t>
   </si>
   <si>
     <t>Usuario</t>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>Depende del sato seleccionado anteriormente(IPS)</t>
-  </si>
-  <si>
-    <t>Autorizaciones  -&gt;   Legalizacion preaprobadas</t>
   </si>
   <si>
     <t>IPS  -&gt; Solicitud de Servicios</t>
@@ -896,15 +893,45 @@
   <si>
     <t>Número de Direccionamiento</t>
   </si>
+  <si>
+    <t>Dia inicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mes inicio </t>
+  </si>
+  <si>
+    <t>Año inicio</t>
+  </si>
+  <si>
+    <t>Dia fin</t>
+  </si>
+  <si>
+    <t>Mes fin</t>
+  </si>
+  <si>
+    <t>Año fin</t>
+  </si>
+  <si>
+    <t>enero</t>
+  </si>
+  <si>
+    <t>febrero</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Descargar  Actualizacion</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1248,7 +1275,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1257,7 +1284,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1270,7 +1297,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1279,18 +1305,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="3" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1302,7 +1328,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1313,7 +1339,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1341,7 +1366,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
@@ -1365,9 +1389,14 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1386,11 +1415,6 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Énfasis1" xfId="3" builtinId="30"/>
@@ -1399,7 +1423,95 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1416,20 +1528,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1517,7 +1616,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1605,7 +1704,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1633,7 +1732,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1664,7 +1763,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1699,11 +1798,11 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Estilo de tabla 1" pivot="0" count="0"/>
+    <tableStyle name="Estilo de tabla 1" pivot="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1717,81 +1816,93 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:C4" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="A1:C4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:C4" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="A1:C4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Inicio de Sesión Portal"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Inicio de Sesión Portal"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Columna2"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="E1:G4" totalsRowShown="0" headerRowDxfId="13" tableBorderDxfId="12" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="E1:G4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla2" displayName="Tabla2" ref="E1:G4" totalsRowShown="0" headerRowDxfId="17" tableBorderDxfId="16" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="E1:G4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Ingreso IPS"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Ingreso IPS"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Columna2"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla3" displayName="Tabla3" ref="I1:K4" totalsRowShown="0" headerRowDxfId="11" tableBorderDxfId="10" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="I1:K4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla3" displayName="Tabla3" ref="I1:K4" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="I1:K4" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Autorizacion Estado Afiliacion "/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Autorizacion Estado Afiliacion "/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Columna2"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabla4" displayName="Tabla4" ref="M1:O14" totalsRowShown="0" headerRowDxfId="9" tableBorderDxfId="8" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="M1:O14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla4" displayName="Tabla4" ref="M1:O14" totalsRowShown="0" headerRowDxfId="13" tableBorderDxfId="12" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="M1:O14" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Autorizaciones Urgencias Medicas" dataCellStyle="20% - Énfasis1"/>
-    <tableColumn id="2" name="Columna1" dataDxfId="7"/>
-    <tableColumn id="3" name="Columna2" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Autorizaciones Urgencias Medicas" dataCellStyle="20% - Énfasis1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Columna1" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Columna2" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabla5" displayName="Tabla5" ref="Q1:S14" totalsRowShown="0" headerRowDxfId="5" tableBorderDxfId="4" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="Q1:S14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla5" displayName="Tabla5" ref="Q1:S14" totalsRowShown="0" headerRowDxfId="9" tableBorderDxfId="8" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="Q1:S14" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Autorizaciones Urgencias Odóntologicas " dataCellStyle="20% - Énfasis1"/>
-    <tableColumn id="2" name="Columna1" dataDxfId="3"/>
-    <tableColumn id="3" name="Columna2" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Autorizaciones Urgencias Odóntologicas " dataCellStyle="20% - Énfasis1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Columna1" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Columna2" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla6" displayName="Tabla6" ref="U1:W5" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="1" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="U1:W5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabla6" displayName="Tabla6" ref="U1:W5" totalsRowShown="0" headerRowDxfId="5" tableBorderDxfId="4" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="U1:W5" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Autorizaciones Consulta Direccionamiento"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Autorizaciones Consulta Direccionamiento"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{EDC74514-DEFB-438B-B93A-44A4A33D283D}" name="Tabla7" displayName="Tabla7" ref="Y1:AA8" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="2" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="Y1:AA8" xr:uid="{EDC74514-DEFB-438B-B93A-44A4A33D283D}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{CABF5565-4FF3-48A8-AD10-184F5130D4D2}" name="Descargar  Actualizacion" dataCellStyle="20% - Énfasis1"/>
+    <tableColumn id="2" xr3:uid="{68060387-DD31-4E46-A92F-1DBE9DB6D951}" name="Columna1" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{1A5FD144-2B54-47A5-9E83-A60370F4743D}" name="Columna2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1829,7 +1940,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1863,6 +1974,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1897,9 +2009,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2072,49 +2185,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="91" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="92"/>
       <c r="C1" s="92"/>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="33" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="10"/>
@@ -2129,9 +2242,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AA92"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2163,1397 +2276,1393 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
-      <c r="A1" s="82" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A1" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="79" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="E1" s="84" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="84" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" s="84" t="s">
+        <v>219</v>
+      </c>
+      <c r="J1" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="K1" s="84" t="s">
+        <v>214</v>
+      </c>
+      <c r="M1" s="84" t="s">
+        <v>220</v>
+      </c>
+      <c r="N1" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="O1" s="84" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q1" s="84" t="s">
+        <v>221</v>
+      </c>
+      <c r="R1" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="S1" s="84" t="s">
+        <v>214</v>
+      </c>
+      <c r="U1" s="84" t="s">
+        <v>225</v>
+      </c>
+      <c r="V1" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="W1" s="84" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y1" s="84" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z1" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA1" s="84" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="83" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="I3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="C1" s="82" t="s">
-        <v>217</v>
-      </c>
-      <c r="E1" s="87" t="s">
-        <v>218</v>
-      </c>
-      <c r="F1" s="87" t="s">
-        <v>216</v>
-      </c>
-      <c r="G1" s="87" t="s">
-        <v>217</v>
-      </c>
-      <c r="I1" s="87" t="s">
-        <v>222</v>
-      </c>
-      <c r="J1" s="87" t="s">
-        <v>216</v>
-      </c>
-      <c r="K1" s="87" t="s">
-        <v>217</v>
-      </c>
-      <c r="M1" s="87" t="s">
-        <v>223</v>
-      </c>
-      <c r="N1" s="87" t="s">
-        <v>216</v>
-      </c>
-      <c r="O1" s="87" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q1" s="87" t="s">
-        <v>224</v>
-      </c>
-      <c r="R1" s="87" t="s">
-        <v>216</v>
-      </c>
-      <c r="S1" s="87" t="s">
-        <v>217</v>
-      </c>
-      <c r="U1" s="87" t="s">
-        <v>228</v>
-      </c>
-      <c r="V1" s="87" t="s">
-        <v>216</v>
-      </c>
-      <c r="W1" s="87" t="s">
-        <v>217</v>
-      </c>
-      <c r="Y1" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z1" s="94"/>
-      <c r="AA1" s="94"/>
-    </row>
-    <row r="2" spans="1:27">
-      <c r="A2" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="U2" s="97" t="s">
-        <v>15</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA2" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="15">
-      <c r="A3" s="84" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="86" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="G3" s="9"/>
-      <c r="I3" s="86" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="25" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="9"/>
-      <c r="M3" s="86" t="s">
-        <v>8</v>
+      <c r="M3" s="83" t="s">
+        <v>6</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="86" t="s">
-        <v>8</v>
+      <c r="O3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="83" t="s">
+        <v>6</v>
       </c>
       <c r="R3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="U3" s="84" t="s">
+      <c r="S3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" s="81" t="s">
+        <v>226</v>
+      </c>
+      <c r="V3" s="15">
+        <v>34567894567</v>
+      </c>
+      <c r="W3" s="16"/>
+      <c r="Y3" s="83" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z3" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA3" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="47"/>
+      <c r="E4" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="M4" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="O4" s="17"/>
+      <c r="Q4" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="S4" s="17"/>
+      <c r="U4" s="82"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="17"/>
+      <c r="Y4" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA4" s="17"/>
+    </row>
+    <row r="5" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="I5" s="22"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="32"/>
+      <c r="M5" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="N5" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="17"/>
+      <c r="Q5" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="R5" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="S5" s="17"/>
+      <c r="U5" s="82"/>
+      <c r="V5" s="89"/>
+      <c r="W5" s="90"/>
+      <c r="Y5" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="V3" s="16">
-        <v>34567894567</v>
-      </c>
-      <c r="W3" s="17"/>
-      <c r="Y3" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="15">
-      <c r="A4" s="85" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="C4" s="48"/>
-      <c r="E4" s="46" t="s">
+      <c r="Z5" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="AA5" s="2"/>
+    </row>
+    <row r="6" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="M6" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="N6" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="Q6" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="R6" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="S6" s="17"/>
+      <c r="Y6" s="83" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA6" s="2"/>
+    </row>
+    <row r="7" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="M7" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="N7" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="O7" s="17"/>
+      <c r="Q7" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="R7" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="S7" s="17"/>
+      <c r="Y7" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="AA7" s="2"/>
+    </row>
+    <row r="8" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="M8" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="N8" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="O8" s="47"/>
+      <c r="Q8" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="R8" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="S8" s="47"/>
+      <c r="Y8" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z8" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="AA8" s="30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="C9" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M9" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="N9" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="17"/>
+      <c r="Q9" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="R9" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" s="17"/>
+    </row>
+    <row r="10" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="M10" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="N10" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="O10" s="17"/>
+      <c r="Q10" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="R10" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="S10" s="17"/>
+    </row>
+    <row r="11" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="M11" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="N11" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="O11" s="17"/>
+      <c r="Q11" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="R11" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="S11" s="17"/>
+    </row>
+    <row r="12" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="M12" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="N12" s="69" t="s">
+        <v>137</v>
+      </c>
+      <c r="O12" s="17"/>
+      <c r="Q12" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="R12" s="69" t="s">
+        <v>137</v>
+      </c>
+      <c r="S12" s="17"/>
+    </row>
+    <row r="13" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="M13" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="N13" s="26"/>
+      <c r="O13" s="17"/>
+      <c r="Q13" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="R13" s="26"/>
+      <c r="S13" s="17"/>
+    </row>
+    <row r="14" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="M14" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="N14" s="86" t="s">
+        <v>224</v>
+      </c>
+      <c r="O14" s="87"/>
+      <c r="Q14" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="R14" s="86" t="s">
+        <v>223</v>
+      </c>
+      <c r="S14" s="87"/>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="93" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" s="88" t="s">
-        <v>220</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" s="11"/>
-      <c r="M4" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="O4" s="18"/>
-      <c r="Q4" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="R4" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="S4" s="18"/>
-      <c r="U4" s="85"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="18"/>
-      <c r="Y4" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA4" s="18"/>
-    </row>
-    <row r="5" spans="1:27" ht="15">
-      <c r="I5" s="23"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="33"/>
-      <c r="M5" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="N5" s="70" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="18"/>
-      <c r="Q5" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="R5" s="70" t="s">
-        <v>108</v>
-      </c>
-      <c r="S5" s="18"/>
-      <c r="U5" s="85"/>
-      <c r="V5" s="98"/>
-      <c r="W5" s="99"/>
-      <c r="Y5" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA5" s="2"/>
-    </row>
-    <row r="6" spans="1:27" ht="15">
-      <c r="M6" s="46" t="s">
-        <v>178</v>
-      </c>
-      <c r="N6" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="O6" s="18"/>
-      <c r="Q6" s="46" t="s">
-        <v>178</v>
-      </c>
-      <c r="R6" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="S6" s="18"/>
-      <c r="Y6" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA6" s="31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="15">
-      <c r="M7" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="N7" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="O7" s="18"/>
-      <c r="Q7" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="R7" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="S7" s="18"/>
-    </row>
-    <row r="8" spans="1:27" ht="15">
-      <c r="M8" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="N8" s="70" t="s">
-        <v>177</v>
-      </c>
-      <c r="O8" s="48"/>
-      <c r="Q8" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="R8" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="S8" s="48"/>
-    </row>
-    <row r="9" spans="1:27" ht="15">
-      <c r="C9" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="M9" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="N9" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="O9" s="18"/>
-      <c r="Q9" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="R9" s="70" t="s">
-        <v>36</v>
-      </c>
-      <c r="S9" s="18"/>
-    </row>
-    <row r="10" spans="1:27" ht="15">
-      <c r="M10" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="N10" s="70" t="s">
-        <v>182</v>
-      </c>
-      <c r="O10" s="18"/>
-      <c r="Q10" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="R10" s="70" t="s">
-        <v>182</v>
-      </c>
-      <c r="S10" s="18"/>
-    </row>
-    <row r="11" spans="1:27" ht="15">
-      <c r="M11" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="N11" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="O11" s="18"/>
-      <c r="Q11" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="R11" s="70" t="s">
-        <v>188</v>
-      </c>
-      <c r="S11" s="18"/>
-    </row>
-    <row r="12" spans="1:27" ht="15">
-      <c r="M12" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="N12" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="O12" s="18"/>
-      <c r="Q12" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="R12" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="S12" s="18"/>
-    </row>
-    <row r="13" spans="1:27" ht="15">
-      <c r="M13" s="46" t="s">
-        <v>172</v>
-      </c>
-      <c r="N13" s="70"/>
-      <c r="O13" s="18"/>
-      <c r="Q13" s="46" t="s">
-        <v>172</v>
-      </c>
-      <c r="R13" s="70"/>
-      <c r="S13" s="18"/>
-    </row>
-    <row r="14" spans="1:27" ht="15">
-      <c r="M14" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="N14" s="89" t="s">
-        <v>227</v>
-      </c>
-      <c r="O14" s="90"/>
-      <c r="Q14" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="R14" s="89" t="s">
-        <v>226</v>
-      </c>
-      <c r="S14" s="90"/>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1"/>
-    <row r="22" spans="1:15">
-      <c r="A22" s="93" t="s">
-        <v>20</v>
       </c>
       <c r="B22" s="94"/>
       <c r="C22" s="94"/>
       <c r="E22" s="93" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F22" s="94"/>
       <c r="G22" s="94"/>
       <c r="I22" s="93" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J22" s="94"/>
       <c r="K22" s="94"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M23" s="93" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N23" s="94"/>
       <c r="O23" s="94"/>
     </row>
-    <row r="24" spans="1:15" ht="15">
-      <c r="A24" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="26" t="s">
+    <row r="24" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>1</v>
       </c>
       <c r="C24" s="9"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="26"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="25"/>
       <c r="G24" s="9"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="26"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="25"/>
       <c r="K24" s="9"/>
       <c r="M24" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="15">
-      <c r="A25" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="25" t="s">
+    </row>
+    <row r="25" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="14"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="14"/>
+      <c r="M25" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="N25" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="O25" s="9"/>
+    </row>
+    <row r="26" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="20"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="13"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="13"/>
+      <c r="M26" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="N26" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" s="14"/>
+    </row>
+    <row r="27" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="11"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="11"/>
+      <c r="M27" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="N27" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="O27" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="14"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="14"/>
-      <c r="M25" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="N25" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="O25" s="9"/>
-    </row>
-    <row r="26" spans="1:15" ht="15">
-      <c r="A26" s="21" t="s">
+      <c r="B28" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="11"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="11"/>
+      <c r="M28" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O28" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B29" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C29" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="14"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="14"/>
+      <c r="M29" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="O29" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="11"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="11"/>
+      <c r="M30" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="N30" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="O30" s="17"/>
+    </row>
+    <row r="31" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="11"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="11"/>
+      <c r="M31" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="N31" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="O31" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="9"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="9"/>
+      <c r="M32" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="O32" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="47"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="47"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="47"/>
+      <c r="M33" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="N33" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="O33" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="14"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="14"/>
+      <c r="M34" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="N34" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="O34" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="C35" s="46"/>
+      <c r="M35" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="N35" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="O35" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="C36" s="46"/>
+      <c r="M36" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="N36" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="O36" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M37" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="N37" s="50"/>
+      <c r="O37" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M38" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="N38" s="47"/>
+      <c r="O38" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M39" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="N39" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="O39" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M40" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="N40" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="O40" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A41" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="N41" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="O41" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" s="39"/>
+      <c r="C42" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="13"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="13"/>
-      <c r="M26" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="N26" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="14"/>
-    </row>
-    <row r="27" spans="1:15" ht="15">
-      <c r="A27" s="22" t="s">
+      <c r="M42" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="O42" s="53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A43" s="41"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="N43" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="O43" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M44" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="O44" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A45" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="15"/>
+      <c r="C45" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="M45" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="O45" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A46" s="39"/>
+      <c r="C46" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="M46" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="O46" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A47" s="39"/>
+      <c r="C47" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M47" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="N47" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="O47" s="47"/>
+    </row>
+    <row r="48" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A48" s="39"/>
+      <c r="C48" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="M48" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="O48" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A49" s="39"/>
+      <c r="C49" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="M49" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="O49" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A50" s="39"/>
+      <c r="C50" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M50" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="O50" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A51" s="41"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="M51" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="O51" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M52" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O52" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A53" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="N53" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="O53" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A54" s="41"/>
+      <c r="B54" s="42"/>
+      <c r="C54" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="M54" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="N54" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="O54" s="2"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M55" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="N55" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="O55" s="2"/>
+    </row>
+    <row r="56" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M56" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="N56" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="O56" s="2"/>
+    </row>
+    <row r="57" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A57" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="M57" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="N57" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="O57" s="2"/>
+    </row>
+    <row r="58" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A58" s="39"/>
+      <c r="C58" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="M58" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="N58" s="55" t="s">
+        <v>144</v>
+      </c>
+      <c r="O58" s="2"/>
+    </row>
+    <row r="59" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A59" s="39"/>
+      <c r="C59" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="M59" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="N59" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="O59" s="2"/>
+    </row>
+    <row r="60" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A60" s="41"/>
+      <c r="B60" s="42"/>
+      <c r="C60" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="M60" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="N60" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O60" s="52"/>
+    </row>
+    <row r="61" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M61" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="N61" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="O61" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M62" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A63" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="M63" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A64" s="39"/>
+      <c r="C64" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="M64" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="N64" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="O64" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A65" s="39"/>
+      <c r="C65" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="N65" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="O65" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A66" s="41"/>
+      <c r="B66" s="42"/>
+      <c r="C66" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="M66" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="N66" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="O66" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M67" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O67" s="52"/>
+    </row>
+    <row r="68" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M68" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="N68" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="O68" s="59" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C69" s="54" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C70" s="54" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C71" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A73" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="11"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="11"/>
-      <c r="M27" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="N27" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="O27" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="15">
-      <c r="A28" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="11"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="11"/>
-      <c r="M28" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O28" s="18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="15">
-      <c r="A29" s="23" t="s">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A74" s="39"/>
+      <c r="C74" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A75" s="39"/>
+      <c r="C75" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A76" s="39"/>
+      <c r="C76" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="14"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="14"/>
-      <c r="M29" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="N29" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="O29" s="18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="15">
-      <c r="A30" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="11"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="11"/>
-      <c r="M30" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="N30" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="O30" s="18"/>
-    </row>
-    <row r="31" spans="1:15" ht="15">
-      <c r="A31" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="11"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="11"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="11"/>
-      <c r="M31" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="N31" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="O31" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="15">
-      <c r="A32" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="9"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="9"/>
-      <c r="M32" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="N32" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="O32" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="15">
-      <c r="A33" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="48"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="48"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="48"/>
-      <c r="M33" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="N33" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="O33" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="15">
-      <c r="A34" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="14"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="14"/>
-      <c r="M34" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="N34" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="O34" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="15">
-      <c r="C35" s="47"/>
-      <c r="M35" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="N35" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="O35" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="15">
-      <c r="C36" s="47"/>
-      <c r="M36" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="N36" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="O36" s="18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="15">
-      <c r="M37" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="N37" s="51"/>
-      <c r="O37" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15">
-      <c r="M38" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="N38" s="48"/>
-      <c r="O38" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="15">
-      <c r="M39" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="N39" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="O39" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="15">
-      <c r="M40" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="N40" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="O40" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="15">
-      <c r="A41" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="M41" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="N41" s="56" t="s">
-        <v>123</v>
-      </c>
-      <c r="O41" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="15">
-      <c r="A42" s="40"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="M42" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="N42" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="O42" s="54" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="15">
-      <c r="A43" s="42"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="M43" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="N43" s="57" t="s">
-        <v>119</v>
-      </c>
-      <c r="O43" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="15">
-      <c r="M44" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="O44" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="15">
-      <c r="A45" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="39" t="s">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A77" s="39"/>
+      <c r="C77" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M45" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="N45" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="O45" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="15">
-      <c r="A46" s="40"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="41" t="s">
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A78" s="39"/>
+      <c r="C78" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M46" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="O46" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="15">
-      <c r="A47" s="40"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="41" t="s">
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A79" s="41"/>
+      <c r="B79" s="42"/>
+      <c r="C79" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="M47" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O47" s="48"/>
-    </row>
-    <row r="48" spans="1:15" ht="15">
-      <c r="A48" s="40"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="M48" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="O48" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="15">
-      <c r="A49" s="40"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="M49" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="N49" s="58" t="s">
-        <v>133</v>
-      </c>
-      <c r="O49" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="15">
-      <c r="A50" s="40"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="M50" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="O50" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="15">
-      <c r="A51" s="42"/>
-      <c r="B51" s="43"/>
-      <c r="C51" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="M51" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="N51" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="O51" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="15">
-      <c r="M52" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="N52" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="O52" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="15">
-      <c r="A53" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="16"/>
-      <c r="C53" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="M53" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="N53" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="O53" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="15">
-      <c r="A54" s="42"/>
-      <c r="B54" s="43"/>
-      <c r="C54" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="M54" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="N54" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="O54" s="2"/>
-    </row>
-    <row r="55" spans="1:15" ht="15">
-      <c r="M55" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="N55" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="O55" s="2"/>
-    </row>
-    <row r="56" spans="1:15" ht="15">
-      <c r="M56" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="N56" s="56" t="s">
-        <v>146</v>
-      </c>
-      <c r="O56" s="2"/>
-    </row>
-    <row r="57" spans="1:15" ht="15">
-      <c r="A57" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="B57" s="16"/>
-      <c r="C57" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="M57" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="N57" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="O57" s="2"/>
-    </row>
-    <row r="58" spans="1:15" ht="15">
-      <c r="A58" s="40"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="M58" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="N58" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="O58" s="2"/>
-    </row>
-    <row r="59" spans="1:15" ht="15">
-      <c r="A59" s="40"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="41" t="s">
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="38" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="39"/>
+      <c r="C82" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="39"/>
+      <c r="C83" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="39"/>
+      <c r="C84" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="41"/>
+      <c r="B85" s="42"/>
+      <c r="C85" s="52" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="39"/>
+      <c r="C88" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="M59" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="N59" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="O59" s="2"/>
-    </row>
-    <row r="60" spans="1:15" ht="15">
-      <c r="A60" s="42"/>
-      <c r="B60" s="43"/>
-      <c r="C60" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="M60" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="N60" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="O60" s="53"/>
-    </row>
-    <row r="61" spans="1:15" ht="15">
-      <c r="M61" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="N61" s="59" t="s">
-        <v>140</v>
-      </c>
-      <c r="O61" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="15">
-      <c r="M62" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="15">
-      <c r="A63" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="B63" s="16"/>
-      <c r="C63" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="M63" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="15">
-      <c r="A64" s="40"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="M64" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="N64" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="O64" s="18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="15">
-      <c r="A65" s="40"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M65" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="N65" s="56" t="s">
-        <v>141</v>
-      </c>
-      <c r="O65" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="15">
-      <c r="A66" s="42"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="M66" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="N66" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="O66" s="18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="15">
-      <c r="M67" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="N67" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="O67" s="53"/>
-    </row>
-    <row r="68" spans="1:15" ht="15">
-      <c r="M68" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="N68" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="O68" s="61" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
-      <c r="C69" s="55" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
-      <c r="C70" s="55" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
-      <c r="C71" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15">
-      <c r="A73" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="B73" s="16"/>
-      <c r="C73" s="71" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15">
-      <c r="A74" s="40"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15">
-      <c r="A75" s="40"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
-      <c r="A76" s="40"/>
-      <c r="B76" s="15"/>
-      <c r="C76" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
-      <c r="A77" s="40"/>
-      <c r="B77" s="15"/>
-      <c r="C77" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15">
-      <c r="A78" s="40"/>
-      <c r="B78" s="15"/>
-      <c r="C78" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15">
-      <c r="A79" s="42"/>
-      <c r="B79" s="43"/>
-      <c r="C79" s="44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="B81" s="16"/>
-      <c r="C81" s="39" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="40"/>
-      <c r="B82" s="15"/>
-      <c r="C82" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="40"/>
-      <c r="B83" s="15"/>
-      <c r="C83" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="40"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="2" t="s">
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="39"/>
+      <c r="C89" s="40" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="42"/>
-      <c r="B85" s="43"/>
-      <c r="C85" s="53" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="39"/>
+      <c r="C90" s="40" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="45" t="s">
-        <v>170</v>
-      </c>
-      <c r="B87" s="16"/>
-      <c r="C87" s="39" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="39"/>
+      <c r="C91" s="40" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="40"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="41" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="40"/>
-      <c r="B89" s="15"/>
-      <c r="C89" s="41" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="41"/>
+      <c r="B92" s="42"/>
+      <c r="C92" s="43" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="40"/>
-      <c r="B90" s="15"/>
-      <c r="C90" s="41" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="40"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="41" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="42"/>
-      <c r="B92" s="43"/>
-      <c r="C92" s="44" t="s">
-        <v>190</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="M23:O23"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="Y1:AA1"/>
     <mergeCell ref="E22:G22"/>
     <mergeCell ref="I22:K22"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27 J27 F27">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27 J27 F27" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$C$41:$C$43</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B28 J28 F28">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B28 J28 F28" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>$C$45:$C$51</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B29 J29 F29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B29 J29 F29" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>$C$53:$C$54</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N31">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N31" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>$C$57:$C$60</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N33">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N33" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>$C$63:$C$66</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="N9 R9">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="N9 R9" xr:uid="{00000000-0002-0000-0100-000005000000}">
       <formula1>$C$73:$C$79</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="N10 R10">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="N10 R10" xr:uid="{00000000-0002-0000-0100-000006000000}">
       <formula1>$C$81:$C$85</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="N11 R11">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="N11 R11" xr:uid="{00000000-0002-0000-0100-000007000000}">
       <formula1>$C$87:$C$92</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <tableParts count="6">
+  <tableParts count="7">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
     <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -3563,159 +3672,159 @@
     <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="93" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
       <c r="E1" s="93" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F1" s="94"/>
       <c r="G1" s="94"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="70" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="71" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>200</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="72" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="26"/>
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="71" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="72" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="72" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="77" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="78" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="74" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="75" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="75" t="s">
         <v>195</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="74" t="s">
-        <v>202</v>
-      </c>
-      <c r="B4" s="76" t="s">
-        <v>210</v>
-      </c>
-      <c r="C4" s="75" t="s">
-        <v>203</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="70"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="74" t="s">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="76" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="74" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="75" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="76" t="s">
         <v>204</v>
-      </c>
-      <c r="B5" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="C5" s="75" t="s">
-        <v>205</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="F5" s="70"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="B6" s="70" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" s="75" t="s">
-        <v>213</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="F6" s="70"/>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="74" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="70" t="s">
-        <v>212</v>
-      </c>
-      <c r="C7" s="75" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="80" t="s">
-        <v>208</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C8" s="81" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="77" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="78" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="78" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="79" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="77" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="78" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="79" t="s">
-        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3724,10 +3833,10 @@
     <mergeCell ref="E1:G1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B3">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$A$12:$A$15</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B8">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>$A$18:$A$20</formula1>
     </dataValidation>
   </dataValidations>
@@ -3737,44 +3846,44 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B3:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="77.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="95" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="96"/>
+      <c r="D3" s="60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="63" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4" s="63" t="s">
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="64" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C5" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D5" s="63" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="67" t="s">
-        <v>161</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -3786,44 +3895,44 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="77.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="95" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C3" s="96"/>
-      <c r="D3" s="62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4" s="63" t="s">
+      <c r="D3" s="60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="64" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4" s="65" t="s">
+      <c r="C5" s="67" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="63" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="69" t="s">
-        <v>165</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
